--- a/data/intermediate/Oryzae_kegg.xlsx
+++ b/data/intermediate/Oryzae_kegg.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="1575">
   <si>
     <t xml:space="preserve">NAME</t>
   </si>
@@ -2259,6 +2259,9 @@
   </si>
   <si>
     <t xml:space="preserve">H(+) (energy metabolism)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">energy_C00080</t>
   </si>
   <si>
     <t xml:space="preserve">H2O</t>
@@ -8099,2737 +8102,2737 @@
         <v>748</v>
       </c>
       <c r="B384" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B385" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B386" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B387" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B388" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B389" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B390" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B391" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B392" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B393" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B394" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B395" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B396" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B397" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B398" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B399" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B400" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B401" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B402" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B403" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B404" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B405" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B406" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B407" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B408" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B409" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B410" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B411" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B412" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B413" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B414" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B415" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B416" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B417" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B418" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B419"/>
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B420"/>
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B421" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B422" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B423" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B424" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B425"/>
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B426" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B427"/>
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B428" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B429" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B430" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B431" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B432" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B433" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B434" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B435"/>
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B436" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B437" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B438" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B439" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B440" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B441" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B442" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B443" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B444" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B445" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B446" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B447" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B448" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B449" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B450" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B451" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B452" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B453" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B454" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B455" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B456" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B457" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B458" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B459" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B460"/>
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B461" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B462"/>
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B463" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B464"/>
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B465" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B466"/>
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B467" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B468"/>
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B469" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B470" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B471" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B472" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B473" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B474" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B475" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B476" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B477" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B478" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B479" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B480" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B481" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B482" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B483" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B484" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B485" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B486" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B487" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B488" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B489" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B490" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B491"/>
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B492" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B493" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B494" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B495"/>
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B496" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B497" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B498" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B499" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B500" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B501" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B502"/>
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B503"/>
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B504" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B505" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B506" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B507" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B508" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B509" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B510" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B511" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B512" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B513" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B514" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B515" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B516" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B517" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B518" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B519" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B520" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B521" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B522" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B523" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B524" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B525" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B526" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B527" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B528" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B529" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B530" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B531" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B532" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B533" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B534" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B535" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B536" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B537" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B538" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B539" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B540" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B541" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B542" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B543" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B544" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B545" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B546" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B547" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B548" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B549" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B550" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B551" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B552" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B553" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B554" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B555" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B556" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B557" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B558"/>
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B559" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B560" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B561" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B562" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B563" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B564"/>
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B565" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B566" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B567" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B568" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B569" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B570" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B571" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B572" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B573" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B574" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B575" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B576" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B577" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B578" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B579" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B580" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B581" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B582" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B583" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B584" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B585" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B586" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B587" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B588" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B589" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B590" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B591" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B592"/>
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B593" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B594" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B595" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B596" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B597" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B598" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B599" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B600" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B601" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B602" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B603" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B604" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B605" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B606" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B607" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B608" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B609" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B610" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B611"/>
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B612" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B613" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B614" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B615" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B616" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B617" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B618" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B619"/>
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B620" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B621" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B622" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B623" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B624" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B625" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B626" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B627" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B628" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B629" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B630" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B631" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B632" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B633" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B634" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B635" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B636"/>
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B637" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B638" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B639" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B640" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B641" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B642" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B643" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B644" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B645" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B646" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B647" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B648" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B649" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B650" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B651" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B652" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B653" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B654" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B655" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B656" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B657" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B658" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B659"/>
     </row>
     <row r="660">
       <c r="A660" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B660" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B661" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B662" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B663" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B664" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B665" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B666" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B667"/>
     </row>
     <row r="668">
       <c r="A668" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B668" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B669" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B670" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B671" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B672" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B673" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B674" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B675" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B676" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B677" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B678" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B679" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B680" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B681" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B682" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B683" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B684" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B685" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B686" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B687" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B688" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B689" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B690" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B691" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B692" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B693" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B694" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B695" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B696" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B697" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B698" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B699" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B700" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B701" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B702" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B703" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B704" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B705" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B706" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B707" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B708" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B709" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B710" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B711" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B712" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B713" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B714" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B715" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B716" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B717" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B718" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="B719"/>
     </row>
     <row r="720">
       <c r="A720" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B720" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B721" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B722" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B723" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B724" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B725" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B726" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B727" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B728" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B729" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B730" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B731" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="732">
@@ -10842,10 +10845,10 @@
     </row>
     <row r="733">
       <c r="A733" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B733" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="734">
@@ -10890,18 +10893,18 @@
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B739" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B740" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="741">
@@ -10922,10 +10925,10 @@
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B743" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="744">
@@ -10978,18 +10981,18 @@
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B750" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B751" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="752">
@@ -11074,10 +11077,10 @@
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B762" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="763">
@@ -11250,26 +11253,26 @@
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B784" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B785" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B786" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="787">
@@ -11282,498 +11285,498 @@
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B788" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B789" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B790" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B791" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B792" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B793" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B794" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B795" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B796" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B797" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B798" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B799" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B800" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B801" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B802" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B803" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B804" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B805" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B806" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B807" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B808" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B809" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B810" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B811" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B812" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B813" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B814" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B815" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B816" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B817" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B818" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B819" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B820" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B821" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B822" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B823" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B824" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B825" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B826" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B827" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B828" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B829" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B830" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B831" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B832" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B833" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B834" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B835" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B836" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B837" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B838" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B839" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B840" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B841" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B842" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B843" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B844" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B845" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B846" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B847" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B848" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B849" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="850">
@@ -11794,10 +11797,10 @@
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B852" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="853">
@@ -11826,10 +11829,10 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B856" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="857">
@@ -11842,18 +11845,18 @@
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B858" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B859" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="860">
@@ -11946,10 +11949,10 @@
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B871" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="872">
@@ -12010,26 +12013,26 @@
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B879" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B880" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B881" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="882">
@@ -12048,26 +12051,26 @@
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B884" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B885" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B886" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="887">
@@ -12086,26 +12089,26 @@
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B889" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B890" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B891" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="892">
@@ -12126,26 +12129,26 @@
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B894" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B895" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B896" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="897">
@@ -12164,26 +12167,26 @@
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B899" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B900" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B901" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="902">
@@ -12196,18 +12199,18 @@
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B903" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B904" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="905">
@@ -12220,26 +12223,26 @@
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B906" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B907" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B908" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="909">
@@ -12252,26 +12255,26 @@
     </row>
     <row r="910">
       <c r="A910" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B910" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B911" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B912" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="913">
@@ -12324,10 +12327,10 @@
     </row>
     <row r="919">
       <c r="A919" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B919" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="920">
@@ -12364,10 +12367,10 @@
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B924" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="925">
@@ -12388,10 +12391,10 @@
     </row>
     <row r="927">
       <c r="A927" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B927" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="928">
@@ -12420,18 +12423,18 @@
     </row>
     <row r="931">
       <c r="A931" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B931" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B932" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="933">
@@ -12468,13 +12471,13 @@
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B937"/>
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B938"/>
     </row>
@@ -12488,10 +12491,10 @@
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B940" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="941">
@@ -12512,18 +12515,18 @@
     </row>
     <row r="943">
       <c r="A943" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B943" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B944" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="945">
@@ -12536,10 +12539,10 @@
     </row>
     <row r="946">
       <c r="A946" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B946" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="947">
@@ -12656,7 +12659,7 @@
     </row>
     <row r="961">
       <c r="A961" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B961" t="s">
         <v>747</v>
@@ -12664,1152 +12667,1144 @@
     </row>
     <row r="962">
       <c r="A962" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B962" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B963" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B964" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B965" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B966" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B967" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B968" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B969" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B970" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B971" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B972" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="s">
-        <v>746</v>
+        <v>794</v>
       </c>
       <c r="B973" t="s">
-        <v>747</v>
+        <v>795</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="s">
-        <v>793</v>
+        <v>1521</v>
       </c>
       <c r="B974" t="s">
-        <v>794</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
       <c r="B975" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>1522</v>
+        <v>808</v>
       </c>
       <c r="B976" t="s">
-        <v>1523</v>
+        <v>809</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B977" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="s">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="B978" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="B979" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="B980" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B981" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="B982" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="B983" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="B984" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>848</v>
+        <v>1525</v>
       </c>
       <c r="B985" t="s">
-        <v>849</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>1524</v>
+        <v>851</v>
       </c>
       <c r="B986" t="s">
-        <v>1525</v>
+        <v>852</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="B987" t="s">
-        <v>851</v>
+        <v>866</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="B988" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B989" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="B990" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="s">
-        <v>876</v>
+        <v>1527</v>
       </c>
       <c r="B991" t="s">
-        <v>877</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="s">
-        <v>1526</v>
+        <v>879</v>
       </c>
       <c r="B992" t="s">
-        <v>1527</v>
+        <v>880</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="s">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="B993" t="s">
-        <v>879</v>
+        <v>890</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="s">
-        <v>888</v>
+        <v>914</v>
       </c>
       <c r="B994" t="s">
-        <v>889</v>
+        <v>915</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="B995" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="s">
-        <v>917</v>
+        <v>930</v>
       </c>
       <c r="B996" t="s">
-        <v>918</v>
+        <v>931</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="s">
-        <v>929</v>
+        <v>1529</v>
       </c>
       <c r="B997" t="s">
-        <v>930</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="s">
-        <v>1528</v>
+        <v>958</v>
       </c>
       <c r="B998" t="s">
-        <v>1306</v>
+        <v>959</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="B999" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="s">
-        <v>961</v>
+        <v>1530</v>
       </c>
       <c r="B1000" t="s">
-        <v>962</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="B1001" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="s">
-        <v>1531</v>
+        <v>984</v>
       </c>
       <c r="B1002" t="s">
-        <v>1532</v>
+        <v>985</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B1003" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="s">
-        <v>985</v>
+        <v>1006</v>
       </c>
       <c r="B1004" t="s">
-        <v>986</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B1005" t="s">
         <v>1005</v>
-      </c>
-      <c r="B1005" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="B1006" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="s">
-        <v>1007</v>
+        <v>1415</v>
       </c>
       <c r="B1007" t="s">
-        <v>1008</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="s">
-        <v>1414</v>
+        <v>1534</v>
       </c>
       <c r="B1008" t="s">
-        <v>1415</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="s">
-        <v>1533</v>
+        <v>1536</v>
       </c>
       <c r="B1009" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="B1010" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="s">
-        <v>1537</v>
+        <v>1002</v>
       </c>
       <c r="B1011" t="s">
-        <v>1538</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="s">
-        <v>1001</v>
+        <v>1016</v>
       </c>
       <c r="B1012" t="s">
-        <v>1002</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="B1013" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="B1014" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="B1015" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="s">
-        <v>1027</v>
+        <v>1540</v>
       </c>
       <c r="B1016" t="s">
-        <v>1028</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="s">
-        <v>1539</v>
+        <v>1044</v>
       </c>
       <c r="B1017" t="s">
-        <v>1540</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="B1018" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="B1019" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="B1020" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="B1021" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="B1022" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="B1023" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="B1024" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="B1025" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
       <c r="B1026" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="B1027" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="B1028" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="B1029" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="B1030" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="s">
-        <v>1086</v>
+        <v>1110</v>
       </c>
       <c r="B1031" t="s">
-        <v>1087</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="B1032" t="s">
-        <v>1110</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="B1033" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="s">
-        <v>1123</v>
+        <v>1542</v>
       </c>
       <c r="B1034" t="s">
-        <v>1124</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="s">
-        <v>1541</v>
+        <v>1128</v>
       </c>
       <c r="B1035" t="s">
-        <v>1542</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="B1036" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="B1037" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B1038" t="s">
         <v>1135</v>
-      </c>
-      <c r="B1038" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="s">
-        <v>1133</v>
+        <v>1544</v>
       </c>
       <c r="B1039" t="s">
-        <v>1134</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="s">
-        <v>1543</v>
+        <v>1147</v>
       </c>
       <c r="B1040" t="s">
-        <v>1544</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="s">
-        <v>1146</v>
+        <v>1167</v>
       </c>
       <c r="B1041" t="s">
-        <v>1147</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="s">
-        <v>1166</v>
+        <v>1546</v>
       </c>
       <c r="B1042" t="s">
-        <v>1167</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="s">
-        <v>1545</v>
+        <v>1188</v>
       </c>
       <c r="B1043" t="s">
-        <v>1546</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="B1044" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B1045" t="s">
         <v>1191</v>
-      </c>
-      <c r="B1045" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="s">
-        <v>1189</v>
+        <v>1199</v>
       </c>
       <c r="B1046" t="s">
-        <v>1190</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="B1047" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="B1048" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="s">
-        <v>1206</v>
+        <v>1548</v>
       </c>
       <c r="B1049" t="s">
-        <v>1207</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="s">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="B1050" t="s">
-        <v>1548</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="s">
-        <v>1549</v>
+        <v>1217</v>
       </c>
       <c r="B1051" t="s">
-        <v>1550</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="s">
-        <v>1216</v>
+        <v>1230</v>
       </c>
       <c r="B1052" t="s">
-        <v>1217</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="s">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="B1053" t="s">
-        <v>1230</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="B1054" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B1055" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="s">
-        <v>1247</v>
+        <v>1552</v>
       </c>
       <c r="B1056" t="s">
-        <v>1248</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="s">
-        <v>1551</v>
+        <v>1250</v>
       </c>
       <c r="B1057" t="s">
-        <v>1552</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="B1058" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="s">
-        <v>1253</v>
+        <v>1285</v>
       </c>
       <c r="B1059" t="s">
-        <v>1254</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="s">
-        <v>1284</v>
+        <v>1554</v>
       </c>
       <c r="B1060" t="s">
-        <v>1285</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="s">
-        <v>1553</v>
+        <v>1287</v>
       </c>
       <c r="B1061" t="s">
-        <v>1554</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="s">
-        <v>1286</v>
+        <v>1310</v>
       </c>
       <c r="B1062" t="s">
-        <v>1287</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="s">
-        <v>1309</v>
+        <v>1320</v>
       </c>
       <c r="B1063" t="s">
-        <v>1310</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="s">
-        <v>1319</v>
+        <v>1338</v>
       </c>
       <c r="B1064" t="s">
-        <v>1320</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="s">
-        <v>1337</v>
+        <v>1348</v>
       </c>
       <c r="B1065" t="s">
-        <v>1338</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="s">
-        <v>1347</v>
+        <v>1382</v>
       </c>
       <c r="B1066" t="s">
-        <v>1348</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="s">
-        <v>1381</v>
+        <v>1415</v>
       </c>
       <c r="B1067" t="s">
-        <v>1382</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="s">
-        <v>1414</v>
+        <v>1556</v>
       </c>
       <c r="B1068" t="s">
-        <v>1415</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="B1069" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="B1070" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="s">
-        <v>1559</v>
+        <v>65</v>
       </c>
       <c r="B1071" t="s">
-        <v>1560</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B1072" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B1073" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="B1074" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="B1075" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="s">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="B1076" t="s">
-        <v>153</v>
+        <v>201</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B1077" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="s">
-        <v>202</v>
+        <v>433</v>
       </c>
       <c r="B1078" t="s">
-        <v>203</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B1079" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="s">
-        <v>435</v>
+        <v>692</v>
       </c>
       <c r="B1080" t="s">
-        <v>436</v>
+        <v>693</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="s">
-        <v>692</v>
+        <v>717</v>
       </c>
       <c r="B1081" t="s">
-        <v>693</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="s">
-        <v>717</v>
+        <v>1562</v>
       </c>
       <c r="B1082" t="s">
-        <v>718</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="s">
-        <v>1561</v>
+        <v>651</v>
       </c>
       <c r="B1083" t="s">
-        <v>1562</v>
+        <v>652</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="s">
-        <v>651</v>
+        <v>750</v>
       </c>
       <c r="B1084" t="s">
-        <v>652</v>
+        <v>751</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="s">
-        <v>749</v>
+        <v>782</v>
       </c>
       <c r="B1085" t="s">
-        <v>750</v>
+        <v>783</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="s">
-        <v>781</v>
+        <v>1564</v>
       </c>
       <c r="B1086" t="s">
-        <v>782</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="s">
-        <v>1563</v>
+        <v>808</v>
       </c>
       <c r="B1087" t="s">
-        <v>1564</v>
+        <v>809</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="s">
-        <v>807</v>
+        <v>930</v>
       </c>
       <c r="B1088" t="s">
-        <v>808</v>
+        <v>931</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="s">
-        <v>929</v>
+        <v>1006</v>
       </c>
       <c r="B1089" t="s">
-        <v>930</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="B1090" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B1091" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="s">
-        <v>1003</v>
+        <v>1044</v>
       </c>
       <c r="B1092" t="s">
-        <v>1004</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="B1093" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="s">
-        <v>1045</v>
+        <v>1192</v>
       </c>
       <c r="B1094" t="s">
-        <v>1046</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="s">
-        <v>1191</v>
+        <v>1207</v>
       </c>
       <c r="B1095" t="s">
-        <v>1192</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="s">
-        <v>1206</v>
+        <v>1285</v>
       </c>
       <c r="B1096" t="s">
-        <v>1207</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="s">
-        <v>1284</v>
+        <v>1362</v>
       </c>
       <c r="B1097" t="s">
-        <v>1285</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="s">
-        <v>1361</v>
+        <v>1566</v>
       </c>
       <c r="B1098" t="s">
-        <v>1362</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="s">
-        <v>1565</v>
+        <v>1370</v>
       </c>
       <c r="B1099" t="s">
-        <v>1566</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="s">
-        <v>1369</v>
+        <v>1395</v>
       </c>
       <c r="B1100" t="s">
-        <v>1370</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="s">
-        <v>1394</v>
+        <v>1568</v>
       </c>
       <c r="B1101" t="s">
-        <v>1395</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="s">
-        <v>1567</v>
+        <v>1570</v>
       </c>
       <c r="B1102" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="s">
-        <v>1569</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>1570</v>
-      </c>
+        <v>1572</v>
+      </c>
+      <c r="B1103"/>
     </row>
     <row r="1104">
       <c r="A1104" t="s">
-        <v>1571</v>
-      </c>
-      <c r="B1104"/>
-    </row>
-    <row r="1105">
-      <c r="A1105" t="s">
-        <v>1572</v>
-      </c>
-      <c r="B1105" t="s">
         <v>1573</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>1574</v>
       </c>
     </row>
   </sheetData>
